--- a/docs/ECRMDP_Validation_Report.xlsx
+++ b/docs/ECRMDP_Validation_Report.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09 23:49</t>
+          <t>2026-10-10 00:06</t>
         </is>
       </c>
     </row>
